--- a/outputs/57590.xlsx
+++ b/outputs/57590.xlsx
@@ -208,16 +208,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -417,271 +421,271 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>820</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>66001248</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>66001248</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>29.78</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>595.6</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>1020</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>15097121</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="1" t="n">
         <v>15097121</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>920</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>15.89</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>14618.8</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="3" t="n">
         <v>15214.4</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="0" t="n">
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="0" t="n">
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A26)*($I$2:$I$3))</f>
+      <c r="B26" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A26))</f>
         <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A27)*($I$2:$I$3))</f>
+      <c r="B27" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A27))</f>
         <v>920</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A28)*($I$2:$I$3))</f>
+      <c r="B28" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A28))</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A29)*($I$2:$I$3))</f>
+      <c r="B29" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A29))</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A30)*($I$2:$I$3))</f>
+      <c r="B30" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A30))</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A31)*($I$2:$I$3))</f>
+      <c r="B31" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A31))</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A32)*($I$2:$I$3))</f>
+      <c r="B32" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A32))</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A33)*($I$2:$I$3))</f>
+      <c r="B33" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A33))</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A34)*($I$2:$I$3))</f>
+      <c r="B34" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A34))</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A35)*($I$2:$I$3))</f>
+      <c r="B35" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A35))</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A36)*($I$2:$I$3))</f>
+      <c r="B36" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A36))</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($C$2:$C$3,"mmmm")=A37)*($I$2:$I$3))</f>
+      <c r="B37" s="1" t="n">
+        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A37))</f>
         <v>0</v>
       </c>
     </row>

--- a/outputs/57590.xlsx
+++ b/outputs/57590.xlsx
@@ -586,8 +586,8 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A26))</f>
-        <v>20</v>
+        <f aca="false">SUMIFS(K2:K3,C2:C3,"&gt;="&amp;DATE(2021,1,1),C2:C3,"&lt;="&amp;EOMONTH(DATE(2021,1,1),0))</f>
+        <v>595.6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -595,98 +595,57 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A27))</f>
-        <v>920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A28))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A29))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A30))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A31))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A32))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A33))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A34))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A35))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A36))</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <f aca="false">SUMPRODUCT((I2:I3)*(TEXT(C2:C3,"mmmm")=A37))</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
